--- a/Кибер физ/Laba 1.xlsx
+++ b/Кибер физ/Laba 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filim\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\Programs\Study\Кибер физ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA52DE9F-C912-465F-A173-BE4F02FDBB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2BD555-AA70-4780-959D-0A0A06453781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="3" xr2:uid="{DCA69E11-58C5-4FA6-80FB-32D4EBD5B8CF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" activeTab="3" xr2:uid="{DCA69E11-58C5-4FA6-80FB-32D4EBD5B8CF}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -4130,12 +4130,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D3DFA0-EBAC-4AAB-B5E6-D3A22FC318B6}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -4173,12 +4173,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDF8CFE6-69E1-40E6-9D79-A3D72CBDD5E1}">
   <dimension ref="A1:D95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>6.3051167601469892E-16</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>1</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>2.2067908660514462E-14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>2</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>3.8618840155900309E-13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>3</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>4.5055313515217026E-12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>4</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>3.9423399325814897E-11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>5</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>2.7596379528070431E-10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>6</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>1.6097888058041085E-9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>7</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>8.0489440290205417E-9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>8</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>3.5214130126964874E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C11">
         <v>9</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>1.3694383938264116E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>10</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>4.7930343783924415E-7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>11</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>1.5250563931248676E-6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C14">
         <v>12</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>4.448081146614197E-6</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>13</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>1.1975603087038223E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16">
         <v>14</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>2.9939007717595554E-5</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17">
         <v>15</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>6.9857684674389631E-5</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>16</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>1.5281368522522732E-4</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19">
         <v>17</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>3.1461641075782097E-4</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C20">
         <v>18</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>6.1175413202909637E-4</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>19</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>1.1269155063693879E-3</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C22">
         <v>20</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>1.9721021361464291E-3</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C23">
         <v>21</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>3.2868368935773818E-3</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C24">
         <v>22</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>5.2290586943276526E-3</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C25">
         <v>23</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>7.9572632304986003E-3</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C26">
         <v>24</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>1.1604342211143795E-2</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C27">
         <v>25</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>1.6246079095601315E-2</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C28">
         <v>26</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>2.1869721859463297E-2</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C29">
         <v>27</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>2.8349639447452432E-2</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C30">
         <v>28</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>3.5437049309315544E-2</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C31">
         <v>29</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>4.2768852614691176E-2</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C32">
         <v>30</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>4.9896994717139688E-2</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C33">
         <v>31</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>5.6335316616125453E-2</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C34">
         <v>32</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>6.1616752548887217E-2</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C35">
         <v>33</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>6.5351101188213703E-2</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C36">
         <v>34</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>6.7273192399631782E-2</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C37">
         <v>35</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>6.7273192399631768E-2</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C38">
         <v>36</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>6.5404492610753096E-2</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C39">
         <v>37</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>6.1869114631793481E-2</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C40">
         <v>38</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>5.698471084507295E-2</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C41">
         <v>39</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>5.1140125117373147E-2</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C42">
         <v>40</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>4.4747609477701497E-2</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C43">
         <v>41</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>3.8199178822428133E-2</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C44">
         <v>42</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>3.1832649018690089E-2</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C45">
         <v>43</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>2.5910295712887287E-2</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C46">
         <v>44</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>2.0610462498887611E-2</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C47">
         <v>45</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>1.6030359721357034E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>7</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>0.93239381990594827</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C51">
         <v>1</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>6.5267567393416381E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C52">
         <v>2</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>2.2843648587695738E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C53">
         <v>3</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>5.3301846704623389E-5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C54">
         <v>4</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>9.3278231733090931E-7</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C55">
         <v>5</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>1.3058952442632731E-8</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C56">
         <v>6</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>1.5235444516404855E-10</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C57">
         <v>7</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>1.5235444516404855E-12</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C58">
         <v>8</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>1.333101395185425E-14</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C59">
         <v>9</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>1.0368566406997751E-16</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C60">
         <v>10</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>7.2579964848984253E-19</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C61">
         <v>11</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>4.618725035844453E-21</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C62">
         <v>12</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>2.6942562709092641E-23</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C63">
         <v>13</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>1.4507533766434502E-25</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C64">
         <v>14</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>7.2537668832172513E-28</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C65">
         <v>15</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>3.3850912121680505E-30</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C66">
         <v>16</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>1.4809774053235222E-32</v>
       </c>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C67">
         <v>17</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>6.0981422572145039E-35</v>
       </c>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C68">
         <v>18</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>2.3714997666945296E-37</v>
       </c>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C69">
         <v>19</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>8.7371044036114266E-40</v>
       </c>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C70">
         <v>20</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>3.0579865412639994E-42</v>
       </c>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C71">
         <v>21</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>1.0193288470879998E-44</v>
       </c>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C72">
         <v>22</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>3.2433190589163632E-47</v>
       </c>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C73">
         <v>23</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>9.8709710488758863E-50</v>
       </c>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C74">
         <v>24</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>2.8790332225888009E-52</v>
       </c>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C75">
         <v>25</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>8.0612930232486443E-55</v>
       </c>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C76">
         <v>26</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>2.1703481216438652E-57</v>
       </c>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C77">
         <v>27</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>5.6268284635211348E-60</v>
       </c>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C78">
         <v>28</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>1.4067071158802837E-62</v>
       </c>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C79">
         <v>29</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>3.3954999348834437E-65</v>
       </c>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C80">
         <v>30</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>7.9228331813947011E-68</v>
       </c>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C81">
         <v>31</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>1.7890268474117064E-70</v>
       </c>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C82">
         <v>32</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>3.9134962287131093E-73</v>
       </c>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C83">
         <v>33</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>8.3013556366641703E-76</v>
       </c>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C84">
         <v>34</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>1.7091026310779182E-78</v>
       </c>
     </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C85">
         <v>35</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>3.4182052621558362E-81</v>
       </c>
     </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C86">
         <v>36</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>6.6465102319696794E-84</v>
       </c>
     </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C87">
         <v>37</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>1.2574478817239937E-86</v>
       </c>
     </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C88">
         <v>38</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>2.3163513610705155E-89</v>
       </c>
     </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C89">
         <v>39</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>4.1575537249983598E-92</v>
       </c>
     </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C90">
         <v>40</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>7.2757190187471301E-95</v>
       </c>
     </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C91">
         <v>41</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>1.2421959300299985E-97</v>
       </c>
     </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C92">
         <v>42</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>2.0703265500499968E-100</v>
       </c>
     </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C93">
         <v>43</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>3.3702990349651115E-103</v>
       </c>
     </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C94">
         <v>44</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>5.361839373808131E-106</v>
       </c>
     </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C95">
         <v>45</v>
       </c>
@@ -5055,9 +5055,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4562B299-3BEE-4D63-9928-3C42FB2DE9DE}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>0.05</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>0.22119921692859512</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>0.1</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>0.39346934028736658</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>0.15</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>0.52763344725898531</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>0.2</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>0.63212055882855767</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>0.25</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>0.71349520313980985</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>0.3</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>0.77686983985157021</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>0.35</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0.82622605654955483</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>0.4</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>0.8646647167633873</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>0.45</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>0.89460077543813565</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>0.5</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>0.91791500137610116</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>0.55000000000000004</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>0.93607213879329243</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>0.6</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>0.95021293163213605</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>0.65</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>0.96122579216827797</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>0.7</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>0.96980261657768152</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>0.75</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>0.97648225414399092</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>0.8</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>0.98168436111126578</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>0.85</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>0.98573576609100078</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>0.9</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>0.98889100346175773</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>0.95</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>0.99134830479687941</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>1</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>0.99326205300091452</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -5271,7 +5271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>7</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>0.05</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>0.29531191028128656</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>0.1</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>0.50341469620859058</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>0.15</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>0.65006225088884473</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>0.2</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>0.75340303605839354</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>0.25</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>0.82622605654955483</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>0.3</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>0.87754357174701814</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>0.35</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>0.91370641350062942</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>0.4</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>0.93918993737478207</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>0.45</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>0.95714787313295979</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>0.5</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>0.96980261657768152</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>0.55000000000000004</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>0.97872026356162289</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>0.6</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>0.9850044231795223</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>0.65</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>0.98943279561614739</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>0.7</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>0.99255341692907562</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>0.75</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>0.99475248160081864</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>0.8</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>0.99630213628351705</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>0.85</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>0.99739415948159149</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>0.9</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>0.9981636952229711</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>0.95</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>0.99870597789453419</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>1</v>
       </c>
@@ -5472,12 +5472,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D425A8F-715E-485D-8DCE-944F327FC4F7}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>20+B2+C2</f>
         <v>32</v>
@@ -5509,16 +5509,16 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <f>B2/100</f>
-        <v>0.05</v>
+        <f>(B2/100)*60</f>
+        <v>3</v>
       </c>
       <c r="E2">
         <f>C2</f>
         <v>7</v>
       </c>
       <c r="F2">
-        <f>(E2*D2)^A2/FACT(A2)*EXP(-E2*D2)</f>
-        <v>6.8865642461685157E-51</v>
+        <f>((E2*D2)^A2)/(FACT(A2))*EXP(-(E2*D2))</f>
+        <v>5.8974132939230593E-3</v>
       </c>
     </row>
   </sheetData>
